--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -493,10 +493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC-profilvalidator</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC-profilvalidator · drivs av IccProfLib</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -643,9 +643,321 @@
         <v>Fel:</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Konvertera till XML</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Konvertera till JSON</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Konvertera till ICC</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Konverterar till XML…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Konverterar till JSON…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Konverterar till ICC…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Läs in ICC-profil</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Släppzon för ICC-profilfiler</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Inga taggar hittades.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Taggnamn</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Storlek</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Utfyllnad</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Byte ändrade sedan inläsning</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Array av {type}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(Inget innehåll)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Läser in fullständig beskrivning…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Ingen valideringsutdata</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -869,95 +869,175 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>indrag</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>sortera nycklar</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -821,223 +821,239 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>Giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>Varning</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>Fel</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>Okänd</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>Utlöst av</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>Fält</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>Aktuellt värde</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>Krävs: 0</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>Ogiltigt</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>Stäng</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>sortera nycklar</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -845,215 +845,263 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>Giltig</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>Varning</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>Fel</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>Okänd</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>Utlöst av</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>Fält</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>Krävs: 0</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>Ogiltigt</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>Stäng</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>indrag</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>sortera nycklar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,503 +605,591 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>Rådata</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>Fel:</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>Konvertera till XML</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>Konvertera till JSON</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>Konvertera till ICC</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>Konverterar till XML…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>Konverterar till JSON…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>Konverterar till ICC…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>Läs in ICC-profil</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>Profil-ID</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>Taggnamn</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>Offset</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>Storlek</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>Utfyllnad</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>Typ</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>Array av {type}</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>byte</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>Profilen är giltig</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>Giltig</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>Varning</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>Fel</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>Okänd</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>Utlöst av</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>Fält</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>Aktuellt värde</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>Krävs: 0</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>Ogiltigt</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>Stäng</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>indrag</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>sortera nycklar</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -637,23 +637,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -669,7 +669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -677,7 +677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -685,7 +685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -693,7 +693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -701,7 +701,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -709,7 +709,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -717,479 +717,495 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>Fel:</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>Konvertera till XML</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>Profil-ID</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>Taggnamn</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>Offset</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>Storlek</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>Utfyllnad</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>Typ</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>Array av {type}</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>byte</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>Profilen är giltig</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>Giltig</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>Varning</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>Fel</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>Okänd</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>Utlöst av</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>Fält</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>Aktuellt värde</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>Krävs: 0</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>Ogiltigt</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>Stäng</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>sortera nycklar</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -512,12 +512,12 @@
         <v>specification using the</v>
       </c>
       <c r="B14" t="str">
-        <v>med referensimplementeringen</v>
+        <v>med demoimplementeringen</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
         <v>.</v>
@@ -525,687 +525,919 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>Validerar…</v>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>Spara ICC-profil</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● Ändrad — osparad</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>eller</v>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>Välj fil</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>Rubrik</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>Taggar</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>Validering</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>Rådata</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>Fel:</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>Konvertera till XML</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>Profil-ID</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>Taggnamn</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>Offset</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>Storlek</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>Utfyllnad</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>Typ</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>Array av {type}</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>(Inget innehåll)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>byte</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>Profilen är giltig</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>Giltig</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>Varning</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>Fel</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>Okänd</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Utlöst av</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>Fält</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>Aktuellt värde</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>Krävs: 0</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>Ogiltigt</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>Stäng</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>indrag</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>sortera nycklar</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Okänd valideringsstatus</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Kritiskt — visas endast för granskning</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -861,583 +861,575 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>Fel:</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>Konvertera till XML</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>Profil-ID</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>Taggnamn</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>Offset</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>Storlek</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>Utfyllnad</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>Typ</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>Array av {type}</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>(Inget innehåll)</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>byte</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>Profilen är giltig</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>Giltig</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>Varning</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>Fel</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>Okänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>Godkänd</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>Underkänd</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>Utlöst av</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>Fält</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>Aktuellt värde</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>Krävs: 0</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>Ogiltigt</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>Stäng</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>indrag</v>
+        <v>sortera nycklar</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>sortera nycklar</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -477,959 +477,983 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>Hjälp</v>
+        <v>Talformat</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>Kontakt</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
+        <v>Hjälp</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>med demoimplementeringen</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>.</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v>Baserat på demoimplementeringen</v>
+        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>med demoimplementeringen</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>Validerar…</v>
+        <v>.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>Spara ICC-profil</v>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● Ändrad — osparad</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>eller</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>Välj fil</v>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>Rubrik</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>Taggar</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>Validering</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>Diagram</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>Rådata</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>Kurvor</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>Ingångskurvor</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>Utgångskurvor</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>CLUT-bild</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>Gamut-bild</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>Kromaticitet</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>Spridningsdiagram</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>Tonkurva</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>Kurvtabell</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>Tabeller</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>Data</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>Utvärdera</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>Läser in…</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>Ingång</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>Utgång</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>Flyttal</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>Normaliserad</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>Läsbar</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>Enhet → PCS</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → Enhet</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>Läser in…</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>Säkerhet</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>Överensstämmelse</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>Kvalitet</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>RAPPORT</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>UNDERKÄND</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>kontroller</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>Fel:</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>Konvertera till XML</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>Konvertera till JSON</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>Profil-ID</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>Taggnamn</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>Offset</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>Storlek</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>Utfyllnad</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>Typ</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>Array av {type}</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>byte</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>Profilen är giltig</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>Giltig</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>Varning</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>Fel</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>Okänd</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>Godkänd</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>Underkänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>Utlöst av</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>Fält</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>Aktuellt värde</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>Krävs: 0</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>Ogiltigt</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>Stäng</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>indrag</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>sortera nycklar</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -885,575 +885,583 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>Säkerhet</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>Överensstämmelse</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>Kvalitet</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>RAPPORT</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>Fel:</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -645,823 +645,1215 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>Diagram</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>Rådata</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>Kurvor</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>Ingångskurvor</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>Utgångskurvor</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>CLUT-bild</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>Gamut-bild</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>Kromaticitet</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Kanaler med många omkastningar visar bara de {shown} största efter ΔL*.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>Tonkurva</v>
+        <v>Visa fler ({n})</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>Kurvtabell</v>
+        <v>Alla</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>Tabeller</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>Data</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>Utvärdera</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>Läser in…</v>
+        <v>L*-tonomkastning</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>Ingång</v>
+        <v>Att lägga till mer färg ska aldrig göra en färg ljusare. Varje enhetskanal sveps medan de andra hålls fasta; varje steg där L* stiger flaggas. Algoritmen kommer ursprungligen från Harold Boll.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>Utgång</v>
+        <v>Den här profilen saknar en enhet→PCS-CLUT, så L*-omkastningsanalysen är inte tillämplig (t.ex. en matris-/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>Flyttal</v>
+        <v>LUT-tabell</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>Rutnätspunkt</v>
+        <v>ΔL*-tröskel (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>Normaliserad</v>
+        <v>{n} omkastningar över ε = {eps}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>Läsbar</v>
+        <v>Inga L*-omkastningar över ε = {eps}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>Enhet → PCS</v>
+        <v>Kanal</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → Enhet</v>
+        <v>Färg (låg → hög)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>Läser in…</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>Säkerhet</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>Överensstämmelse</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>Kvalitet</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>RAPPORT</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>UNDERKÄND</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>kontroller</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>Fel:</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>Konvertera till XML</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>Profil-ID</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>Taggnamn</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>Offset</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>Storlek</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>Utfyllnad</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>Typ</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>Array av {type}</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>byte</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>Profilen är giltig</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>Giltig</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>Varning</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>Fel</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>Okänd</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>Godkänd</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>Underkänd</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>Utlöst av</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>Fält</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>Aktuellt värde</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>Krävs: 0</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>Förväntat: {value}</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>Ogiltigt</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>Stäng</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>indrag</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>sortera nycklar</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Inga taggar hittades.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Taggnamn</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Storlek</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Utfyllnad</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Byte ändrade sedan inläsning</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Array av {type}</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(Inget innehåll)</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Läser in fullständig beskrivning…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Ingen valideringsutdata</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Profilen är giltig</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Profilen har varning(ar)</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Profilen följer inte specifikationen</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Kritiskt valideringsfel</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Okänd valideringsstatus</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Kritiskt — visas endast för granskning</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,1343 +517,1415 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Användarhandbok</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
+        <v>Sök i handboken</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>med demoimplementeringen</v>
+        <v>Sök i användarhandboken</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>.</v>
+        <v>Föregående träff</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v>Baserat på demoimplementeringen</v>
+        <v>Nästa träff</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Stäng handboken</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>Validerar…</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>Spara ICC-profil</v>
+        <v>Det gick inte att läsa in användarhandboken.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● Ändrad — osparad</v>
+        <v>Inga</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>eller</v>
+        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>Välj fil</v>
+        <v>med demoimplementeringen</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>Rubrik</v>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>Taggar</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>Validering</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>Analys</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>Renderingsavsikt</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% färg</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>Perceptuell</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>Mättnad</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>Kanaler med många omkastningar visar bara de {shown} största efter ΔL*.</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa fler ({n})</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>Alla</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>Analyserar…</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>Analys</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>L*-tonomkastning</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>Att lägga till mer färg ska aldrig göra en färg ljusare. Varje enhetskanal sveps medan de andra hålls fasta; varje steg där L* stiger flaggas. Algoritmen kommer ursprungligen från Harold Boll.</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>Den här profilen saknar en enhet→PCS-CLUT, så L*-omkastningsanalysen är inte tillämplig (t.ex. en matris-/TRC-skärmprofil).</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>LUT-tabell</v>
+        <v>Kanaler med många omkastningar visar bara de {shown} största efter ΔL*.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>ΔL*-tröskel (ε)</v>
+        <v>Visa fler ({n})</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>{n} omkastningar över ε = {eps}</v>
+        <v>Alla</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>Inga L*-omkastningar över ε = {eps}</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>Kanal</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>Färg (låg → hög)</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>Diagram</v>
+        <v>L*-tonomkastning</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>Rådata</v>
+        <v>Att lägga till mer färg ska aldrig göra en färg ljusare. Varje enhetskanal sveps medan de andra hålls fasta; varje steg där L* stiger flaggas. Algoritmen kommer ursprungligen från Harold Boll.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>Den här profilen saknar en enhet→PCS-CLUT, så L*-omkastningsanalysen är inte tillämplig (t.ex. en matris-/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>LUT-tabell</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>Kurvor</v>
+        <v>ΔL*-tröskel (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>Ingångskurvor</v>
+        <v>{n} omkastningar över ε = {eps}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>Utgångskurvor</v>
+        <v>Inga L*-omkastningar över ε = {eps}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>CLUT-bild</v>
+        <v>Kanal</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>Gamut-bild</v>
+        <v>Färg (låg → hög)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>Kromaticitet</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>Tonkurva</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>Kurvtabell</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tabeller</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Data</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>Utvärdera</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>Läser in…</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>Ingång</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>Utgång</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Flyttal</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>Normaliserad</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>Läsbar</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>Enhet → PCS</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → Enhet</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>Läser in…</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>Säkerhet</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>Överensstämmelse</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>Kvalitet</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>RAPPORT</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>UNDERKÄND</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>kontroller</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>Prenumerera</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>Stäng</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>E-postadress</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>du@exempel.com</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>(valfritt)</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>Avbryt</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>Prenumerera</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>Stäng</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>Fel:</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>Konvertera till XML</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>Profil-ID</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>Taggnamn</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>Offset</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>Storlek</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>Utfyllnad</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>Typ</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>Array av {type}</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>byte</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>Profilen är giltig</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>Giltig</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>Varning</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>Fel</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>Okänd</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>Godkänd</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>Underkänd</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>Utlöst av</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>Fält</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>Aktuellt värde</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>Krävs: 0</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>Ogiltigt</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>Stäng</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>indrag</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>sortera nycklar</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -797,330 +797,330 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>Kanaler med många omkastningar visar bara de {shown} största efter ΔL*.</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>Visa fler ({n})</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>Alla</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>Analyserar…</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>Analys</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>L*-tonomkastning</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>Att lägga till mer färg ska aldrig göra en färg ljusare. Varje enhetskanal sveps medan de andra hålls fasta; varje steg där L* stiger flaggas. Algoritmen kommer ursprungligen från Harold Boll.</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>Den här profilen saknar en enhet→PCS-CLUT, så L*-omkastningsanalysen är inte tillämplig (t.ex. en matris-/TRC-skärmprofil).</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>LUT-tabell</v>
+        <v>max</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>ΔL*-tröskel (ε)</v>
+        <v>Kanaler med många omkastningar visar bara de {shown} största efter ΔL*.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>{n} omkastningar över ε = {eps}</v>
+        <v>Visa fler ({n})</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>Inga L*-omkastningar över ε = {eps}</v>
+        <v>Alla</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>Kanal</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>Färg (låg → hög)</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>Diagram</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>Rådata</v>
+        <v>L*-tonomkastning</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>Att lägga till mer färg ska aldrig göra en färg ljusare. Varje enhetskanal sveps medan de andra hålls fasta; varje steg där L* stiger flaggas. Algoritmen kommer ursprungligen från Harold Boll.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>Den här profilen saknar en enhet→PCS-CLUT, så L*-omkastningsanalysen är inte tillämplig (t.ex. en matris-/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>Kurvor</v>
+        <v>LUT-tabell</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>Ingångskurvor</v>
+        <v>ΔL*-tröskel (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>Utgångskurvor</v>
+        <v>{n} omkastningar över ε = {eps}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>CLUT-bild</v>
+        <v>Inga L*-omkastningar över ε = {eps}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>Gamut-bild</v>
+        <v>Kanal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>Kromaticitet</v>
+        <v>Färg (låg → hög)</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>Tonkurva</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>Kurvtabell</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>Tabeller</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>Data</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>Utvärdera</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>Läser in…</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>Ingång</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>Utgång</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>Flyttal</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>Normaliserad</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>Läsbar</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>Enhet → PCS</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → Enhet</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="91">
@@ -1133,799 +1133,879 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>Säkerhet</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>Överensstämmelse</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>Kvalitet</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>RAPPORT</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>UNDERKÄND</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>kontroller</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>Prenumerera</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>Stäng</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>E-postadress</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>du@exempel.com</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>(valfritt)</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>Avbryt</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>Prenumerera</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>Stäng</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>Fel:</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>Konvertera till XML</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>Konvertera till JSON</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>Profil-ID</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>Taggnamn</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>Offset</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>Storlek</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>Utfyllnad</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>Typ</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>Array av {type}</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>byte</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>Profilen är giltig</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>Giltig</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>Varning</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>Fel</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>Okänd</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>Godkänd</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>Underkänd</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>Utlöst av</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>Fält</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>Aktuellt värde</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>Krävs: 0</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>Ogiltigt</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>Stäng</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>indrag</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>sortera nycklar</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -877,474 +877,474 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>Kanaler med många omkastningar visar bara de {shown} största efter ΔL*.</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>Visa fler ({n})</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>Alla</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>Analyserar…</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>Analys</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>L*-tonomkastning</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>Att lägga till mer färg ska aldrig göra en färg ljusare. Varje enhetskanal sveps medan de andra hålls fasta; varje steg där L* stiger flaggas. Algoritmen kommer ursprungligen från Harold Boll.</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Den här profilen saknar en enhet→PCS-CLUT, så L*-omkastningsanalysen är inte tillämplig (t.ex. en matris-/TRC-skärmprofil).</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>LUT-tabell</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>ΔL*-tröskel (ε)</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>{n} omkastningar över ε = {eps}</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>Inga L*-omkastningar över ε = {eps}</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>Kanal</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>Färg (låg → hög)</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>Diagram</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>Rådata</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Kurvor</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>Ingångskurvor</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>Utgångskurvor</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>CLUT-bild</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>Gamut-bild</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>Kromaticitet</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>Tonkurva</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>Kurvtabell</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>Tabeller</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>Data</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>Utvärdera</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>Läser in…</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>Ingång</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>Utgång</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>Flyttal</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>Normaliserad</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>Läsbar</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>Enhet → PCS</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → Enhet</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>Läser in…</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Säkerhet</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>Överensstämmelse</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>Kvalitet</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>RAPPORT</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>UNDERKÄND</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>kontroller</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="119">
@@ -1357,18 +1357,18 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="122">
@@ -1381,631 +1381,535 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>E-postadress</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>du@exempel.com</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>(valfritt)</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>Avbryt</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>Prenumerera</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>Stäng</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>Fel:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>Konvertera till XML</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>Profil-ID</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>Taggnamn</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>Offset</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>Storlek</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>Utfyllnad</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>Typ</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>Array av {type}</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>byte</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>Profilen är giltig</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>Giltig</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>Varning</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>Fel</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>Okänd</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>Godkänd</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Underkänd</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>Utlöst av</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>Fält</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>Aktuellt värde</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Krävs: 0</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>Förväntat: {value}</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>Ogiltigt</v>
+        <v>sortera nycklar</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>Stäng</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>Läser in XML-redigeraren…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>Läser in JSON-redigeraren…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● osparade XML-ändringar</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● osparade JSON-ändringar</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>indrag</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>sortera nycklar</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -853,1063 +853,1071 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>medel</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>Analyserar…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>Analys</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>Diagram</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>Rådata</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>Kurvor</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Ingångskurvor</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Utgångskurvor</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>CLUT-bild</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>Gamut-bild</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>Kromaticitet</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>Tonkurva</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>Kurvtabell</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>Tabeller</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>Data</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>Utvärdera</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>Läser in…</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>Ingång</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>Utgång</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>Flyttal</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>Normaliserad</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>Läsbar</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>Enhet → PCS</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → Enhet</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>Läser in…</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>Säkerhet</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>Överensstämmelse</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>Kvalitet</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>RAPPORT</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>E-postadress</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>du@exempel.com</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>(valfritt)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>Avbryt</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>Prenumerera</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>Stäng</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Fel:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,1511 +413,1887 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>Inställningar</v>
+        <v>Tur och retur (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>Visning</v>
+        <v>Tur och retur genom profilens enhetskub, som referensverktyget iccRoundTrip. Tur och retur 1 är felet enhet→PCS→enhet (ΔE*ab); tur och retur 2 mäter stabiliteten i PCS-cykeln. PRMG-histogrammet visar interoperabiliteten mot Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>Bakgrund</v>
+        <v>Använd MPE-taggar (färg)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>Språk</v>
+        <v>Den här profilen kan inte köras tur och retur – den saknar de enhet↔PCS-transformationer som behövs (t.ex. en enkelriktad eller abstrakt profil).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>System</v>
+        <v>Tur och retur hoppades över: enhetens färgrymd är för bred för att utvärdera (för många sampel).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>Ljus</v>
+        <v>Mått</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>Mörk</v>
+        <v>Tur och retur 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>Systemstandard</v>
+        <v>Tur och retur 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>Talformat</v>
+        <v>enhet → PCS → enhet</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>Hexadecimal</v>
+        <v>stabilitet i PCS-cykeln</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Hjälp</v>
+        <v>Medel ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Kontakt</v>
+        <v>Max ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>Användarhandbok</v>
+        <v>Sämsta L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>Sök i handboken</v>
+        <v>Angiven färgrymd</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Sök i användarhandboken</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>Föregående träff</v>
+        <v>Ej angiven</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>Nästa träff</v>
+        <v>Ej utvärderad</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>Stäng handboken</v>
+        <v>PRMG-interoperabilitet</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>Läser in…</v>
+        <v>Tur-och-retur-ΔE</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>Det gick inte att läsa in användarhandboken.</v>
+        <v>Antal</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>Inga</v>
+        <v>Andel</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Totalt</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
+        <v>PRMG ej utvärderad</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>med demoimplementeringen</v>
+        <v>Inställningar</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>.</v>
+        <v>Visning</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v>Baserat på demoimplementeringen</v>
+        <v>Bakgrund</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Språk</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>Validerar…</v>
+        <v>System</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>Spara ICC-profil</v>
+        <v>Ljus</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● Ändrad — osparad</v>
+        <v>Mörk</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>eller</v>
+        <v>Talformat</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>Välj fil</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>Rubrik</v>
+        <v>Hjälp</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>Taggar</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>Validering</v>
+        <v>Användarhandbok</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>Analys</v>
+        <v>Sök i handboken</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>Sök i användarhandboken</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Föregående träff</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Nästa träff</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Stäng handboken</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% färg</v>
+        <v>Det gick inte att läsa in användarhandboken.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>Perceptuell</v>
+        <v>Inga</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>Mättnad</v>
+        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>med demoimplementeringen</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>Profilstatistik</v>
+        <v>.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>medel</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>max</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>Analyserar…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>Analys</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>Diagram</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>Rådata</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>Kurvor</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>Ingångskurvor</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>Utgångskurvor</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>CLUT-bild</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>Gamut-bild</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>Kromaticitet</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>Spridningsdiagram</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>Tonkurva</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>Kurvtabell</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>Tabeller</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>Data</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>Utvärdera</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>Läser in…</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>Ingång</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>Utgång</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>Flyttal</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>Normaliserad</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>Läsbar</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>Enhet → PCS</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → Enhet</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>Läser in…</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>Säkerhet</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>Överensstämmelse</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>Kvalitet</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>RAPPORT</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>UNDERKÄND</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>kontroller</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>Drivs av {lib}</v>
+        <v>max</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>Prenumerera</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>Stäng</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>E-postadress</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>du@exempel.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>(valfritt)</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>Avbryt</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>Prenumerera</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>Stäng</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>Fel:</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>Konvertera till XML</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>Profil-ID</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>Taggnamn</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>Offset</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>Storlek</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>Utfyllnad</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>Typ</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>Array av {type}</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>(Inget innehåll)</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>byte</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>Profilen är giltig</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>Giltig</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>Varning</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>Fel</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>Okänd</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>Godkänd</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>Underkänd</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>Visa i sammanhang</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>Utlöst av</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>Fält</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>Aktuellt värde</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>Krävs: 0</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>Ogiltigt</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>Stäng</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>indrag</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>sortera nycklar</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Storlek</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Utfyllnad</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Byte ändrade sedan inläsning</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Array av {type}</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(Inget innehåll)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Läser in fullständig beskrivning…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Ingen valideringsutdata</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Profilen är giltig</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Profilen har varning(ar)</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Profilen följer inte specifikationen</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Kritiskt valideringsfel</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Okänd valideringsstatus</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Kritiskt — visas endast för granskning</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,1695 +605,2365 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>Inställningar</v>
+        <v>Mätvärden för hela profilen för en renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och ett mått på tur och retur-noggrannheten. Välj renderingsavsikt och typ av tur och retur — tabellen och histogrammet uppdateras därefter.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>Visning</v>
+        <v>Typ av tur och retur</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Bakgrund</v>
+        <v>Påverkar inte denna typ av tur och retur</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>Språk</v>
+        <v>Denna typ av tur och retur är inte tillgänglig för den här profilen.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>System</v>
+        <v>Fördelning av tur och retur-ΔE</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>Ljus</v>
+        <v>Inga tur och retur-prover hamnade inom det utvärderade området.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>Mörk</v>
+        <v>Standardavvikelse</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>Systemstandard</v>
+        <v>Relativ frekvens</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Talformat</v>
+        <v>Kumulativ frekvens</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horisontell skala</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>Decimal</v>
+        <v>Heltals-ΔE</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>Hjälp</v>
+        <v>Autoskala</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>Kontakt</v>
+        <v>Klasser</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>Användarhandbok</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>Sök i handboken</v>
+        <v>Färguppslagstabellen (CLUT) för en enhet↔PCS-transform, utlagd som en bild. Välj vilken renderingsavsikts-tabell som ska visas.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>Sök i användarhandboken</v>
+        <v>Den här profilen har inga CLUT-baserade enhet↔PCS-tabeller att visualisera.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>Föregående träff</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>Nästa träff</v>
+        <v>Gamut-taggens karta över inom/utom gamut: neutral där en PCS-färg är reproducerbar, röd där den hamnar utanför enhetens gamut.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>Stäng handboken</v>
+        <v>Den här profilen har ingen gamut-tagg att visualisera.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>Läser in…</v>
+        <v>Vertikal skala</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>Det gick inte att läsa in användarhandboken.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>Inga</v>
+        <v>Tonökning</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Tonökning (ut − in)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
+        <v>Visa fullständig dump</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>med demoimplementeringen</v>
+        <v>Utdata avkortad av prestandaskäl.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>.</v>
+        <v>Översikt inom gamut (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v>Baserat på demoimplementeringen</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Reproducerbarhet (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>Validerar…</v>
+        <v>PRMG-interoperabilitet</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>Spara ICC-profil</v>
+        <v>iccviz-översikt: ett rutnät av enhetsvärden förs till PCS, tillbaka till enhet och till PCS igen; ΔE*ab mäts mellan de två PCS-passen. En snabb stabilitetskontroll inom gamut.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● Ändrad — osparad</v>
+        <v>iccRoundTrip Tur och retur 1: ΔE*ab mellan varje enhetsfärgs PCS och dess PCS efter en tur och retur Lab → enhet → Lab. Speglar inversionsnoggrannhet och gamutmappning.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip Tur och retur 2: ΔE*ab mellan första och andra tur och retur — hur stabil en upprepad PCS-tur och retur är (reproducerbarhet, oberoende av den första turens gamutklippning).</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG: PCS-färger inom Perceptual Reference Medium Gamut gör en enda tur och retur (Lab → enhet → Lab); ΔE*ab-fördelningen visar interoperabiliteten mellan profiler.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Inställningar</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Visning</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Bakgrund</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Språk</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>System</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Ljus</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Mörk</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Talformat</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Hjälp</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Användarhandbok</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Sök i handboken</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Sök i användarhandboken</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Föregående träff</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Nästa träff</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Stäng handboken</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Det gick inte att läsa in användarhandboken.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>Inga</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>eller</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>Välj fil</v>
+        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>med demoimplementeringen</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>Rubrik</v>
+        <v>.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>Taggar</v>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>Validering</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>Analys</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Profiler</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Visa profilpoolen</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Fäll ihop</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% färg</v>
+        <v>Läs in profiler</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>Perceptuell</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Släpp ICC-profiler här</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>Mättnad</v>
+        <v>eller en bild (TIFF/PNG/JPEG) för att extrahera dess inbäddade profil — filerna stannar på din enhet.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Ny från .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>Profilstatistik</v>
+        <v>Sortera efter namn</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Ny profil från .cube</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Välj .cube-fil</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>Rundtur-ΔE</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>eller släpp den här, eller klistra in nedan</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>medel</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>max</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>Analyserar…</v>
+        <v>Det gick inte att läsa den filen.</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>Analys</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Jämför</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>Diagram</v>
+        <v>Länka</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>Rådata</v>
+        <v>Dra profiler från poolen till den här fliken</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>Ingen profil vald</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>Kurvor</v>
+        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>Ingångskurvor</v>
+        <v>Inget att jämföra ännu</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>Utgångskurvor</v>
+        <v>Dra en eller flera profiler till fliken Jämför.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>CLUT-bild</v>
+        <v>Gamutjämförelse</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>Gamut-bild</v>
+        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>Kromaticitet</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Skal</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>Tonkurva</v>
+        <v>Trådmodell</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Kurvtabell</v>
+        <v>Opacitet</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Tabeller</v>
+        <v>Färg</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Data</v>
+        <v>Enfärgad</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Utvärdera</v>
+        <v>Efter värde</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Läser in…</v>
+        <v>Efter nyans</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Ingång</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Utgång</v>
+        <v>Skivtallrik</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Flyttal</v>
+        <v>Omloppsbana</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Draghastighet</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Normaliserad</v>
+        <v>Rullning</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Läsbar</v>
+        <v>Rullningshastighet</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>Enhet → PCS</v>
+        <v>Bygger gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → Enhet</v>
+        <v>ingen gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Visa/dölj</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Läser in…</v>
+        <v>3D-gamutskal</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>2D-gamutsnitt</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Länkning</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Säkerhet</v>
+        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Överensstämmelse</v>
+        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>Kvalitet</v>
+        <v>V4-skärmskapare</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>RAPPORT</v>
+        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>UNDERKÄND</v>
+        <v>V5 RGB-skärm</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>kontroller</v>
+        <v>släpp en skärmprofil</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>V5-observatör (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>släpp en observatörsprofil</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Skapa V4-skärmprofil</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Prenumerera</v>
+        <v>Profilnamn</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Skapa</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Stäng</v>
+        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>E-postadress</v>
+        <v>{n} fil(er) inte inlästa</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>du@exempel.com</v>
+        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>(valfritt)</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>Avbryt</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>Prenumerera</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>Stäng</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>Fel:</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>Konvertera till XML</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>Profil-ID</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>Taggnamn</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>Storlek</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>Utfyllnad</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>Typ</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>Array av {type}</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>(Inget innehåll)</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>byte</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>Profilen är giltig</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>Giltig</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>Varning</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>Fel</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>Okänd</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>Godkänd</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>Underkänd</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>Utlöst av</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>Fält</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>Aktuellt värde</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>Krävs: 0</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>Ogiltigt</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>Stäng</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>indrag</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>sortera nycklar</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>ICC-profilverktyg</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Drivs av {lib}</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Prenumerera</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Få besked om nya profiletool-versioner</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Få besked om nya versioner</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>E-postadress</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>du@exempel.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Hur kommer du att använda profiletool?</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(valfritt)</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Avbryt</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Prenumerera</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Tack — vi hör av oss.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Integritetsmeddelande</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Ange en giltig e-postadress.</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>För många förfrågningar. Försök igen senare.</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Kontrollera formuläret och försök igen.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Nätverksfel. Försök igen.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Fel:</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Konvertera till XML</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Konvertera till JSON</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Konvertera till ICC</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Konverterar till XML…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Konverterar till JSON…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Konverterar till ICC…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Läs in ICC-profil</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Släppzon för ICC-profilfiler</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Inga taggar hittades.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Taggnamn</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Storlek</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Utfyllnad</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Byte ändrade sedan inläsning</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Array av {type}</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>(Inget innehåll)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Läser in fullständig beskrivning…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Ingen valideringsutdata</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Profilen är giltig</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Profilen har varning(ar)</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Profilen följer inte specifikationen</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Kritiskt valideringsfel</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Okänd valideringsstatus</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Kritiskt — visas endast för granskning</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>Länka</v>
@@ -1299,1671 +1299,2423 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>Dra profiler från poolen till den här fliken</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>Ta bort</v>
+        <v>Dra profiler från poolen till den här fliken</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>Ingen profil vald</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
+        <v>Ingen profil vald</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>Inget att jämföra ännu</v>
+        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>Dra en eller flera profiler till fliken Jämför.</v>
+        <v>Inget att jämföra ännu</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>Gamutjämförelse</v>
+        <v>Dra en eller flera profiler till fliken Jämför.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
+        <v>Gamutjämförelse</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>Skal</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>Trådmodell</v>
+        <v>Skal</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacitet</v>
+        <v>Trådmodell</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>Färg</v>
+        <v>Axelnummer</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>Enfärgad</v>
+        <v>Opacitet</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>Efter värde</v>
+        <v>Färg</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>Efter nyans</v>
+        <v>Enfärgad</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotation</v>
+        <v>Efter värde</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>Skivtallrik</v>
+        <v>Efter nyans</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>Omloppsbana</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>Draghastighet</v>
+        <v>Skivtallrik</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>Rullning</v>
+        <v>Omloppsbana</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Rullningshastighet</v>
+        <v>Draghastighet</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>Bygger gamut…</v>
+        <v>Rullning</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>ingen gamut</v>
+        <v>Rullningshastighet</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>Visa/dölj</v>
+        <v>Bygger gamut…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>3D-gamutskal</v>
+        <v>ingen gamut</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>2D-gamutsnitt</v>
+        <v>Visa/dölj</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>Plan</v>
+        <v>3D-gamutskal</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>2D-gamutsnitt</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>Länkning</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
+        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
+        <v>Länkning</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4-skärmskapare</v>
+        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
+        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB-skärm</v>
+        <v>V4-skärmskapare</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>släpp en skärmprofil</v>
+        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>V5-observatör (PCC)</v>
+        <v>V5 RGB-skärm</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>släpp en observatörsprofil</v>
+        <v>släpp en skärmprofil</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
+        <v>V5-observatör (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Skapa V4-skärmprofil</v>
+        <v>släpp en observatörsprofil</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>Profilnamn</v>
+        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Skapa</v>
+        <v>Skapa V4-skärmprofil</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>Skapar…</v>
+        <v>Profilnamn</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
+        <v>Skapa</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>Avbryt</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n} fil(er) inte inlästa</v>
+        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
+        <v>Länkpipeline</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>OK</v>
+        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>Klar</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>eller</v>
+        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>Välj fil</v>
+        <v>Kontrollerar bild…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>Rubrik</v>
+        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>Taggar</v>
+        <v>Transformera bild</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>Validering</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>Analys</v>
+        <v>Släpp profiler för att starta kedjan</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>borttagen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Flytta tidigare</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Flytta senare</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Flytta upp</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Flytta ner</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% färg</v>
+        <v>Återgivningsalternativ (alla)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>Perceptuell</v>
+        <v>Återgivningsalternativ för denna transformering</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Transformeringarna använder olika återgivningsalternativ</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>Mättnad</v>
+        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>Profilstatistik</v>
+        <v>Kedja</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Kedjan kunde inte analyseras.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Kontrollerar kedja…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Kedjan hänger inte ihop ({detail}).</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>Åtgärda kedjan innan bilder bearbetas</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>medel</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>DeviceLink-namn</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>max</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>Analyserar…</v>
+        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>Analys</v>
+        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Bygg en kedja för att bearbeta bilder</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>Diagram</v>
+        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>Rådata</v>
+        <v>Sparade den transformerade bilden.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>Kunde inte läsa filen.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>Kurvor</v>
+        <v>Datafilen är för stor.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>Ingångskurvor</v>
+        <v>Transformera data</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>Utgångskurvor</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>CLUT-bild</v>
+        <v>Föredra</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>Gamut-bild</v>
+        <v>Observatör</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>Kromaticitet</v>
+        <v>Ljuskälla</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Villkor</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>Tonkurva</v>
+        <v>Filtrera {n} dubblett(er)</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>Kurvtabell</v>
+        <v>median</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>Tabeller</v>
+        <v>medelvärde</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>Data</v>
+        <v>patchar</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>Utvärdera</v>
+        <v>{n} dubbletter</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>Läser in…</v>
+        <v>Transformeringsresultat</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>Ingång</v>
+        <v>{src} → {dst} · {n} patchar</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>Utgång</v>
+        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>Flyttal</v>
+        <v>Spara som</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Spara</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>Normaliserad</v>
+        <v>Invertera transformering</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>Läsbar</v>
+        <v>Inverterar…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>Enhet → PCS</v>
+        <v>Invertera</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → Enhet</v>
+        <v>sista steget</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>första steget</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>Läser in…</v>
+        <v>Data i {in} → sök {out}</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Invertering kräver en kedja med 2–3 profiler</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>ΔE-kostnad</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Denna bild har en inbäddad ICC-profil.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Extrahera och lägg till i kedjan</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Extraherar…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Avfärda</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>Säkerhet</v>
+        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>Överensstämmelse</v>
+        <v>Alternativ för bildutdata</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>Kvalitet</v>
+        <v>Kodning</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>RAPPORT</v>
+        <v>Samma som källan</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>UNDERKÄND</v>
+        <v>8-bitars</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>kontroller</v>
+        <v>16-bitars</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Flyttal (32-bitars)</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Komprimering</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Ingen</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Planformat</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>Prenumerera</v>
+        <v>Sammansatt</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Separerad</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>CMM-interpolation</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>Stäng</v>
+        <v>Tetraedrisk</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Linjär</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>E-postadress</v>
+        <v>Bädda in ICC</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>du@exempel.com</v>
+        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Montera spektral-TIFF</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>(valfritt)</v>
+        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>Avbryt</v>
+        <v>Montera och spara</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>Prenumerera</v>
+        <v>Monterar…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Monterade {n} kanaler.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>Stäng</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>{n} fil(er) inte inlästa</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>Fel:</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>Konvertera till XML</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>Profil-ID</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>Taggnamn</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>Offset</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>Storlek</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>Utfyllnad</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>Typ</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>Array av {type}</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>byte</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>max</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>Profilen är giltig</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>Giltig</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>Varning</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>Fel</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>Okänd</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>Godkänd</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>Underkänd</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>Utlöst av</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>Fält</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>Aktuellt värde</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>Krävs: 0</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>Ogiltigt</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>Stäng</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>indrag</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>sortera nycklar</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Laddar Profile Assessment WG-rapport…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Kör Profile Assessment WG-kontroller…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Profile Assessment WG-rapport</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Säkerhet</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Överensstämmelse</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Kvalitet</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>RAPPORT</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>UNDERKÄND</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>kontroller</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>ICC-profilverktyg</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Drivs av {lib}</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Prenumerera</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Få besked om nya profiletool-versioner</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Få besked om nya versioner</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>E-postadress</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>du@exempel.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Hur kommer du att använda profiletool?</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>(valfritt)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Avbryt</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Prenumerera</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Tack — vi hör av oss.</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Integritetsmeddelande</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Ange en giltig e-postadress.</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>För många förfrågningar. Försök igen senare.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Kontrollera formuläret och försök igen.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Nätverksfel. Försök igen.</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Fel:</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Konvertera till XML</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Konvertera till JSON</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Konvertera till ICC</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Konverterar till XML…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Konverterar till JSON…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Konverterar till ICC…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Läs in ICC-profil</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Släppzon för ICC-profilfiler</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Inga taggar hittades.</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Taggnamn</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Storlek</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Utfyllnad</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Byte ändrade sedan inläsning</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Array av {type}</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>(Inget innehåll)</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Läser in fullständig beskrivning…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Ingen valideringsutdata</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Profilen är giltig</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Profilen har varning(ar)</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Profilen följer inte specifikationen</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Kritiskt valideringsfel</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Okänd valideringsstatus</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Kritiskt — visas endast för granskning</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1053,2669 +1053,2645 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>Ladda upp en ICC-profil för att validera den mot specifikationen</v>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>med demoimplementeringen</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>.</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v>Baserat på demoimplementeringen</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>Validerar…</v>
+        <v>Profiler</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>Spara ICC-profil</v>
+        <v>Visa profilpoolen</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● Ändrad — osparad</v>
+        <v>Fäll ihop</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Profiler</v>
+        <v>Läs in profiler</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>Visa profilpoolen</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>Fäll ihop</v>
+        <v>Släpp ICC-profiler här</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>Läs in profiler</v>
+        <v>eller en bild (TIFF/PNG/JPEG) för att extrahera dess inbäddade profil — filerna stannar på din enhet.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>Ta bort</v>
+        <v>Ny från .cube</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>Släpp ICC-profiler här</v>
+        <v>Sortera efter namn</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>eller en bild (TIFF/PNG/JPEG) för att extrahera dess inbäddade profil — filerna stannar på din enhet.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Ny från .cube</v>
+        <v>Ny profil från .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>Sortera efter namn</v>
+        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>Välj .cube-fil</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>Ny profil från .cube</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Välj .cube-fil</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
         <v>eller släpp den här, eller klistra in nedan</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Avbryt</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Skapa DeviceLink</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Skapar…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>Avbryt</v>
+        <v>Det gick inte att läsa den filen.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>Skapar…</v>
+        <v>Jämför</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>Det gick inte att läsa den filen.</v>
+        <v>Länka</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>Profil</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>Jämför</v>
+        <v>Dra profiler från poolen till den här fliken</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>Länka</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>Spektral</v>
+        <v>Ingen profil vald</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>Dra profiler från poolen till den här fliken</v>
+        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>Ta bort</v>
+        <v>Inget att jämföra ännu</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>Ingen profil vald</v>
+        <v>Dra en eller flera profiler till fliken Jämför.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
+        <v>Gamutjämförelse</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>Inget att jämföra ännu</v>
+        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>Dra en eller flera profiler till fliken Jämför.</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>Gamutjämförelse</v>
+        <v>Skal</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
+        <v>Trådmodell</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Axelnummer</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>Skal</v>
+        <v>Opacitet</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>Trådmodell</v>
+        <v>Färg</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>Axelnummer</v>
+        <v>Enfärgad</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>Opacitet</v>
+        <v>Efter värde</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>Färg</v>
+        <v>Efter nyans</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>Enfärgad</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>Efter värde</v>
+        <v>Skivtallrik</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>Efter nyans</v>
+        <v>Omloppsbana</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>Rotation</v>
+        <v>Draghastighet</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>Skivtallrik</v>
+        <v>Rullning</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>Omloppsbana</v>
+        <v>Rullningshastighet</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>Draghastighet</v>
+        <v>Bygger gamut…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>Rullning</v>
+        <v>ingen gamut</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>Rullningshastighet</v>
+        <v>Visa/dölj</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>Bygger gamut…</v>
+        <v>3D-gamutskal</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>ingen gamut</v>
+        <v>2D-gamutsnitt</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>Visa/dölj</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>3D-gamutskal</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>2D-gamutsnitt</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>Plan</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>Länkning</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
+        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>Länkning</v>
+        <v>V4-skärmskapare</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
+        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
+        <v>V5 RGB-skärm</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>V4-skärmskapare</v>
+        <v>släpp en skärmprofil</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
+        <v>V5-observatör (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 RGB-skärm</v>
+        <v>släpp en observatörsprofil</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>släpp en skärmprofil</v>
+        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>V5-observatör (PCC)</v>
+        <v>Skapa V4-skärmprofil</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>släpp en observatörsprofil</v>
+        <v>Profilnamn</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
+        <v>Skapa</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>Skapa V4-skärmprofil</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>Profilnamn</v>
+        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>Skapa</v>
+        <v>Länkpipeline</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>Skapar…</v>
+        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
+        <v>Klar</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>Länkpipeline</v>
+        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
+        <v>Kontrollerar bild…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>Klar</v>
+        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
+        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>Kontrollerar bild…</v>
+        <v>Transformera bild</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
+        <v>Släpp profiler för att starta kedjan</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>Transformera bild</v>
+        <v>borttagen</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>Transformerar…</v>
+        <v>Flytta tidigare</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>Släpp profiler för att starta kedjan</v>
+        <v>Flytta senare</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>borttagen</v>
+        <v>Flytta upp</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>Flytta tidigare</v>
+        <v>Flytta ner</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>Flytta senare</v>
+        <v>Återgivningsalternativ (alla)</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>Flytta upp</v>
+        <v>Återgivningsalternativ för denna transformering</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>Flytta ner</v>
+        <v>Transformeringarna använder olika återgivningsalternativ</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>Återgivningsalternativ (alla)</v>
+        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>Återgivningsalternativ för denna transformering</v>
+        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>Transformeringarna använder olika återgivningsalternativ</v>
+        <v>Kedja</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
+        <v>Kedjan kunde inte analyseras.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
+        <v>Kontrollerar kedja…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>Kedja</v>
+        <v>Kedjan hänger inte ihop ({detail}).</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Kedjan kunde inte analyseras.</v>
+        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>Kontrollerar kedja…</v>
+        <v>Åtgärda kedjan innan bilder bearbetas</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>Kedjan hänger inte ihop ({detail}).</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>Åtgärda kedjan innan bilder bearbetas</v>
+        <v>DeviceLink-namn</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>Rensa</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>DeviceLink-namn</v>
+        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>Skapar…</v>
+        <v>Bygg en kedja för att bearbeta bilder</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
+        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
+        <v>Sparade den transformerade bilden.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>Bygg en kedja för att bearbeta bilder</v>
+        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
+        <v>Kunde inte läsa filen.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>Sparade den transformerade bilden.</v>
+        <v>Datafilen är för stor.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformera data</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>Kunde inte läsa filen.</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>Datafilen är för stor.</v>
+        <v>Föredra</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>Transformera data</v>
+        <v>Observatör</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>Transformerar…</v>
+        <v>Ljuskälla</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>Föredra</v>
+        <v>Villkor</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>Observatör</v>
+        <v>Filtrera {n} dubblett(er)</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>Ljuskälla</v>
+        <v>median</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>Villkor</v>
+        <v>medelvärde</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>Filtrera {n} dubblett(er)</v>
+        <v>patchar</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>median</v>
+        <v>{n} dubbletter</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>medelvärde</v>
+        <v>Transformeringsresultat</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>patchar</v>
+        <v>{src} → {dst} · {n} patchar</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>{n} dubbletter</v>
+        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>Transformeringsresultat</v>
+        <v>Spara som</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · {n} patchar</v>
+        <v>Spara</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
+        <v>Invertera transformering</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>Spara som</v>
+        <v>Inverterar…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>Spara</v>
+        <v>Invertera</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>Invertera transformering</v>
+        <v>sista steget</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>Inverterar…</v>
+        <v>första steget</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>Invertera</v>
+        <v>Data i {in} → sök {out}</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>sista steget</v>
+        <v>Invertering kräver en kedja med 2–3 profiler</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>första steget</v>
+        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>Data i {in} → sök {out}</v>
+        <v>ΔE-kostnad</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>Invertering kräver en kedja med 2–3 profiler</v>
+        <v>Denna bild har en inbäddad ICC-profil.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
+        <v>Extrahera och lägg till i kedjan</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>ΔE-kostnad</v>
+        <v>Extraherar…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>Denna bild har en inbäddad ICC-profil.</v>
+        <v>Avfärda</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>Extrahera och lägg till i kedjan</v>
+        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>Extraherar…</v>
+        <v>Alternativ för bildutdata</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>Avfärda</v>
+        <v>Kodning</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
+        <v>Samma som källan</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>Alternativ för bildutdata</v>
+        <v>8-bitars</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>Kodning</v>
+        <v>16-bitars</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>Samma som källan</v>
+        <v>Flyttal (32-bitars)</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8-bitars</v>
+        <v>Komprimering</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16-bitars</v>
+        <v>Ingen</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>Flyttal (32-bitars)</v>
+        <v>Planformat</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>Komprimering</v>
+        <v>Sammansatt</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>Ingen</v>
+        <v>Separerad</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>Planformat</v>
+        <v>CMM-interpolation</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>Sammansatt</v>
+        <v>Tetraedrisk</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>Separerad</v>
+        <v>Linjär</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>CMM-interpolation</v>
+        <v>Bädda in ICC</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>Tetraedrisk</v>
+        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>Linjär</v>
+        <v>Montera spektral-TIFF</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>Bädda in ICC</v>
+        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
+        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>Montera spektral-TIFF</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
+        <v>Montera och spara</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
+        <v>Monterar…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>ch</v>
+        <v>Monterade {n} kanaler.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>Montera och spara</v>
+        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>Monterar…</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>Monterade {n} kanaler.</v>
+        <v>{n} fil(er) inte inlästa</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
+        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>Avbryt</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n} fil(er) inte inlästa</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>OK</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>eller</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>Välj fil</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>Rubrik</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>Taggar</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>Validering</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>Analys</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% färg</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>Perceptuell</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>Mättnad</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>Profilstatistik</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>max</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>medel</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>max</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>Analyserar…</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>Analys</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>Diagram</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>Rådata</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>Kurvor</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>Ingångskurvor</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>Utgångskurvor</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>CLUT-bild</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>Gamut-bild</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>Kromaticitet</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>Tonkurva</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>Kurvtabell</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>Tabeller</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>Data</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>Utvärdera</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>Läser in…</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>Ingång</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>Utgång</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>Flyttal</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>Normaliserad</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>Läsbar</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>Enhet → PCS</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → Enhet</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>Läser in…</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>Säkerhet</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>Överensstämmelse</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>Kvalitet</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>RAPPORT</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>UNDERKÄND</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>kontroller</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>Prenumerera</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>Stäng</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>E-postadress</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>du@exempel.com</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>(valfritt)</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>Avbryt</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>Prenumerera</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>Stäng</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>Fel:</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>Konvertera till XML</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>Profil-ID</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>Taggnamn</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>Offset</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>Storlek</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>Utfyllnad</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>Typ</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>Array av {type}</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>byte</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>Profilen är giltig</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>Giltig</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>Varning</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>Fel</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>Okänd</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>Godkänd</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>Underkänd</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>Utlöst av</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>Fält</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>Aktuellt värde</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>Krävs: 0</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>Ogiltigt</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>Stäng</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>sortera nycklar</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>indrag</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>sortera nycklar</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,3285 +413,3293 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>Tur och retur (PRMG)</v>
+        <v>{pct} % av sampelvärdena låg utanför intervallet och klipptes.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>Tur och retur genom profilens enhetskub, som referensverktyget iccRoundTrip. Tur och retur 1 är felet enhet→PCS→enhet (ΔE*ab); tur och retur 2 mäter stabiliteten i PCS-cykeln. PRMG-histogrammet visar interoperabiliteten mot Perceptual Reference Medium Gamut.</v>
+        <v>Tur och retur (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>Använd MPE-taggar (färg)</v>
+        <v>Tur och retur genom profilens enhetskub, som referensverktyget iccRoundTrip. Tur och retur 1 är felet enhet→PCS→enhet (ΔE*ab); tur och retur 2 mäter stabiliteten i PCS-cykeln. PRMG-histogrammet visar interoperabiliteten mot Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>Den här profilen kan inte köras tur och retur – den saknar de enhet↔PCS-transformationer som behövs (t.ex. en enkelriktad eller abstrakt profil).</v>
+        <v>Använd MPE-taggar (färg)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>Tur och retur hoppades över: enhetens färgrymd är för bred för att utvärdera (för många sampel).</v>
+        <v>Den här profilen kan inte köras tur och retur – den saknar de enhet↔PCS-transformationer som behövs (t.ex. en enkelriktad eller abstrakt profil).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>Mått</v>
+        <v>Tur och retur hoppades över: enhetens färgrymd är för bred för att utvärdera (för många sampel).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>Tur och retur 1</v>
+        <v>Mått</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>Tur och retur 2</v>
+        <v>Tur och retur 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>enhet → PCS → enhet</v>
+        <v>Tur och retur 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>stabilitet i PCS-cykeln</v>
+        <v>enhet → PCS → enhet</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>Min ΔE</v>
+        <v>stabilitet i PCS-cykeln</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Medel ΔE</v>
+        <v>Min ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Max ΔE</v>
+        <v>Medel ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>Sämsta L, a, b</v>
+        <v>Max ΔE</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>Angiven färgrymd</v>
+        <v>Sämsta L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Angiven färgrymd</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>Ej angiven</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>Ej utvärderad</v>
+        <v>Ej angiven</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>PRMG-interoperabilitet</v>
+        <v>Ej utvärderad</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>Tur-och-retur-ΔE</v>
+        <v>PRMG-interoperabilitet</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>Antal</v>
+        <v>Tur-och-retur-ΔE</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>Andel</v>
+        <v>Antal</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>Totalt</v>
+        <v>Andel</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG ej utvärderad</v>
+        <v>Totalt</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>Mätvärden för hela profilen för en renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och ett mått på tur och retur-noggrannheten. Välj renderingsavsikt och typ av tur och retur — tabellen och histogrammet uppdateras därefter.</v>
+        <v>PRMG ej utvärderad</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>Typ av tur och retur</v>
+        <v>Mätvärden för hela profilen för en renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och ett mått på tur och retur-noggrannheten. Välj renderingsavsikt och typ av tur och retur — tabellen och histogrammet uppdateras därefter.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Påverkar inte denna typ av tur och retur</v>
+        <v>Typ av tur och retur</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>Denna typ av tur och retur är inte tillgänglig för den här profilen.</v>
+        <v>Påverkar inte denna typ av tur och retur</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>Fördelning av tur och retur-ΔE</v>
+        <v>Denna typ av tur och retur är inte tillgänglig för den här profilen.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>Inga tur och retur-prover hamnade inom det utvärderade området.</v>
+        <v>Fördelning av tur och retur-ΔE</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>Standardavvikelse</v>
+        <v>Inga tur och retur-prover hamnade inom det utvärderade området.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>Relativ frekvens</v>
+        <v>Standardavvikelse</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Kumulativ frekvens</v>
+        <v>Relativ frekvens</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>Horisontell skala</v>
+        <v>Kumulativ frekvens</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>Heltals-ΔE</v>
+        <v>Horisontell skala</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>Autoskala</v>
+        <v>Heltals-ΔE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>Klasser</v>
+        <v>Autoskala</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>CLUT-bild</v>
+        <v>Klasser</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>Färguppslagstabellen (CLUT) för en enhet↔PCS-transform, utlagd som en bild. Välj vilken renderingsavsikts-tabell som ska visas.</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>Den här profilen har inga CLUT-baserade enhet↔PCS-tabeller att visualisera.</v>
+        <v>Färguppslagstabellen (CLUT) för en enhet↔PCS-transform, utlagd som en bild. Välj vilken renderingsavsikts-tabell som ska visas.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>Gamut-bild</v>
+        <v>Den här profilen har inga CLUT-baserade enhet↔PCS-tabeller att visualisera.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>Gamut-taggens karta över inom/utom gamut: neutral där en PCS-färg är reproducerbar, röd där den hamnar utanför enhetens gamut.</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>Den här profilen har ingen gamut-tagg att visualisera.</v>
+        <v>Gamut-taggens karta över inom/utom gamut: neutral där en PCS-färg är reproducerbar, röd där den hamnar utanför enhetens gamut.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>Vertikal skala</v>
+        <v>Den här profilen har ingen gamut-tagg att visualisera.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>Vertikal skala</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>Tonökning</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>Tonökning (ut − in)</v>
+        <v>Tonökning</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>Visa fullständig dump</v>
+        <v>Tonökning (ut − in)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>Utdata avkortad av prestandaskäl.</v>
+        <v>Visa fullständig dump</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>Översikt inom gamut (RT0)</v>
+        <v>Utdata avkortad av prestandaskäl.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Översikt inom gamut (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>Reproducerbarhet (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>PRMG-interoperabilitet</v>
+        <v>Reproducerbarhet (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>iccviz-översikt: ett rutnät av enhetsvärden förs till PCS, tillbaka till enhet och till PCS igen; ΔE*ab mäts mellan de två PCS-passen. En snabb stabilitetskontroll inom gamut.</v>
+        <v>PRMG-interoperabilitet</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip Tur och retur 1: ΔE*ab mellan varje enhetsfärgs PCS och dess PCS efter en tur och retur Lab → enhet → Lab. Speglar inversionsnoggrannhet och gamutmappning.</v>
+        <v>iccviz-översikt: ett rutnät av enhetsvärden förs till PCS, tillbaka till enhet och till PCS igen; ΔE*ab mäts mellan de två PCS-passen. En snabb stabilitetskontroll inom gamut.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Tur och retur 2: ΔE*ab mellan första och andra tur och retur — hur stabil en upprepad PCS-tur och retur är (reproducerbarhet, oberoende av den första turens gamutklippning).</v>
+        <v>iccRoundTrip Tur och retur 1: ΔE*ab mellan varje enhetsfärgs PCS och dess PCS efter en tur och retur Lab → enhet → Lab. Speglar inversionsnoggrannhet och gamutmappning.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG: PCS-färger inom Perceptual Reference Medium Gamut gör en enda tur och retur (Lab → enhet → Lab); ΔE*ab-fördelningen visar interoperabiliteten mellan profiler.</v>
+        <v>iccRoundTrip Tur och retur 2: ΔE*ab mellan första och andra tur och retur — hur stabil en upprepad PCS-tur och retur är (reproducerbarhet, oberoende av den första turens gamutklippning).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>Inställningar</v>
+        <v>iccRoundTrip PRMG: PCS-färger inom Perceptual Reference Medium Gamut gör en enda tur och retur (Lab → enhet → Lab); ΔE*ab-fördelningen visar interoperabiliteten mellan profiler.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>Visning</v>
+        <v>Inställningar</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>Bakgrund</v>
+        <v>Visning</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>Språk</v>
+        <v>Bakgrund</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>System</v>
+        <v>Språk</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>Ljus</v>
+        <v>System</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>Mörk</v>
+        <v>Ljus</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>Systemstandard</v>
+        <v>Mörk</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>Talformat</v>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>Hexadecimal</v>
+        <v>Talformat</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>Hjälp</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>Kontakt</v>
+        <v>Hjälp</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>Användarhandbok</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>Sök i handboken</v>
+        <v>Användarhandbok</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>Sök i användarhandboken</v>
+        <v>Sök i handboken</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>Föregående träff</v>
+        <v>Sök i användarhandboken</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>Nästa träff</v>
+        <v>Föregående träff</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>Stäng handboken</v>
+        <v>Nästa träff</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Läser in…</v>
+        <v>Stäng handboken</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Det gick inte att läsa in användarhandboken.</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>Inga</v>
+        <v>Det gick inte att läsa in användarhandboken.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Inga</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v>Baserat på demoimplementeringen</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>Validerar…</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>Spara ICC-profil</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● Ändrad — osparad</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>Profiler</v>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>Visa profilpoolen</v>
+        <v>Profiler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>Fäll ihop</v>
+        <v>Visa profilpoolen</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>Läs in profiler</v>
+        <v>Fäll ihop</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>Ta bort</v>
+        <v>Läs in profiler</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>Släpp ICC-profiler här</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>eller en bild (TIFF/PNG/JPEG) för att extrahera dess inbäddade profil — filerna stannar på din enhet.</v>
+        <v>Släpp ICC-profiler här</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>Ny från .cube</v>
+        <v>eller en bild (TIFF/PNG/JPEG) för att extrahera dess inbäddade profil — filerna stannar på din enhet.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>Sortera efter namn</v>
+        <v>Ny från .cube</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>Sortera efter namn</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>Ny profil från .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
+        <v>Ny profil från .cube</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>Välj .cube-fil</v>
+        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Välj .cube-fil</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>eller släpp den här, eller klistra in nedan</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Avbryt</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>Skapar…</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>Det gick inte att läsa den filen.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>Profil</v>
+        <v>Det gick inte att läsa den filen.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>Jämför</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>Länka</v>
+        <v>Jämför</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>Spektral</v>
+        <v>Länka</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>Dra profiler från poolen till den här fliken</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>Ta bort</v>
+        <v>Dra profiler från poolen till den här fliken</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>Ingen profil vald</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
+        <v>Ingen profil vald</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>Inget att jämföra ännu</v>
+        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>Dra en eller flera profiler till fliken Jämför.</v>
+        <v>Inget att jämföra ännu</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>Gamutjämförelse</v>
+        <v>Dra en eller flera profiler till fliken Jämför.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
+        <v>Gamutjämförelse</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>Skal</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>Trådmodell</v>
+        <v>Skal</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>Axelnummer</v>
+        <v>Trådmodell</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>Opacitet</v>
+        <v>Axelnummer</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Färg</v>
+        <v>Opacitet</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Enfärgad</v>
+        <v>Färg</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Efter värde</v>
+        <v>Enfärgad</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Efter nyans</v>
+        <v>Efter värde</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Rotation</v>
+        <v>Efter nyans</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Skivtallrik</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Omloppsbana</v>
+        <v>Skivtallrik</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Draghastighet</v>
+        <v>Omloppsbana</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Rullning</v>
+        <v>Draghastighet</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Rullningshastighet</v>
+        <v>Rullning</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Bygger gamut…</v>
+        <v>Rullningshastighet</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>ingen gamut</v>
+        <v>Bygger gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>Visa/dölj</v>
+        <v>ingen gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>3D-gamutskal</v>
+        <v>Visa/dölj</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>2D-gamutsnitt</v>
+        <v>3D-gamutskal</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Plan</v>
+        <v>2D-gamutsnitt</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Länkning</v>
+        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
+        <v>Länkning</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
+        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>V4-skärmskapare</v>
+        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
+        <v>V4-skärmskapare</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB-skärm</v>
+        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>släpp en skärmprofil</v>
+        <v>V5 RGB-skärm</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>V5-observatör (PCC)</v>
+        <v>släpp en skärmprofil</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>släpp en observatörsprofil</v>
+        <v>V5-observatör (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
+        <v>släpp en observatörsprofil</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Skapa V4-skärmprofil</v>
+        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Profilnamn</v>
+        <v>Skapa V4-skärmprofil</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Skapa</v>
+        <v>Profilnamn</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Skapar…</v>
+        <v>Skapa</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Länkpipeline</v>
+        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
+        <v>Länkpipeline</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>Klar</v>
+        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
+        <v>Klar</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>Kontrollerar bild…</v>
+        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
+        <v>Kontrollerar bild…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
+        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>Transformera bild</v>
+        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>Transformerar…</v>
+        <v>Transformera bild</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>Släpp profiler för att starta kedjan</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>borttagen</v>
+        <v>Släpp profiler för att starta kedjan</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>Flytta tidigare</v>
+        <v>borttagen</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>Flytta senare</v>
+        <v>Flytta tidigare</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>Flytta upp</v>
+        <v>Flytta senare</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>Flytta ner</v>
+        <v>Flytta upp</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>Återgivningsalternativ (alla)</v>
+        <v>Flytta ner</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>Återgivningsalternativ för denna transformering</v>
+        <v>Återgivningsalternativ (alla)</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>Transformeringarna använder olika återgivningsalternativ</v>
+        <v>Återgivningsalternativ för denna transformering</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
+        <v>Transformeringarna använder olika återgivningsalternativ</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
+        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>Kedja</v>
+        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>Kedjan kunde inte analyseras.</v>
+        <v>Kedja</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>Kontrollerar kedja…</v>
+        <v>Kedjan kunde inte analyseras.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>Kedjan hänger inte ihop ({detail}).</v>
+        <v>Kontrollerar kedja…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
+        <v>Kedjan hänger inte ihop ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>Åtgärda kedjan innan bilder bearbetas</v>
+        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>Rensa</v>
+        <v>Åtgärda kedjan innan bilder bearbetas</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLink-namn</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>Skapar…</v>
+        <v>DeviceLink-namn</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
+        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>Bygg en kedja för att bearbeta bilder</v>
+        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
+        <v>Bygg en kedja för att bearbeta bilder</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>Sparade den transformerade bilden.</v>
+        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Sparade den transformerade bilden.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>Kunde inte läsa filen.</v>
+        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>Datafilen är för stor.</v>
+        <v>Kunde inte läsa filen.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>Transformera data</v>
+        <v>Datafilen är för stor.</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformerar…</v>
+        <v>Transformera data</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>Föredra</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>Observatör</v>
+        <v>Föredra</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>Ljuskälla</v>
+        <v>Observatör</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>Villkor</v>
+        <v>Ljuskälla</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>Filtrera {n} dubblett(er)</v>
+        <v>Villkor</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>median</v>
+        <v>Filtrera {n} dubblett(er)</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>medelvärde</v>
+        <v>median</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>patchar</v>
+        <v>medelvärde</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>{n} dubbletter</v>
+        <v>patchar</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>Transformeringsresultat</v>
+        <v>{n} dubbletter</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · {n} patchar</v>
+        <v>Transformeringsresultat</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
+        <v>{src} → {dst} · {n} patchar</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>Spara som</v>
+        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>Spara</v>
+        <v>Spara som</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>Invertera transformering</v>
+        <v>Spara</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>Inverterar…</v>
+        <v>Invertera transformering</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>Invertera</v>
+        <v>Inverterar…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>sista steget</v>
+        <v>Invertera</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>första steget</v>
+        <v>sista steget</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>Data i {in} → sök {out}</v>
+        <v>första steget</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>Invertering kräver en kedja med 2–3 profiler</v>
+        <v>Data i {in} → sök {out}</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
+        <v>Invertering kräver en kedja med 2–3 profiler</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>ΔE-kostnad</v>
+        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>Denna bild har en inbäddad ICC-profil.</v>
+        <v>ΔE-kostnad</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Extrahera och lägg till i kedjan</v>
+        <v>Denna bild har en inbäddad ICC-profil.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extraherar…</v>
+        <v>Extrahera och lägg till i kedjan</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>Avfärda</v>
+        <v>Extraherar…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
+        <v>Avfärda</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>Alternativ för bildutdata</v>
+        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>Kodning</v>
+        <v>Alternativ för bildutdata</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>Samma som källan</v>
+        <v>Kodning</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8-bitars</v>
+        <v>Samma som källan</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16-bitars</v>
+        <v>8-bitars</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>Flyttal (32-bitars)</v>
+        <v>16-bitars</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>Komprimering</v>
+        <v>Flyttal (32-bitars)</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>Ingen</v>
+        <v>Komprimering</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>Planformat</v>
+        <v>Ingen</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>Sammansatt</v>
+        <v>Planformat</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>Separerad</v>
+        <v>Sammansatt</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>CMM-interpolation</v>
+        <v>Separerad</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>Tetraedrisk</v>
+        <v>CMM-interpolation</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>Linjär</v>
+        <v>Tetraedrisk</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>Bädda in ICC</v>
+        <v>Linjär</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
+        <v>Bädda in ICC</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>Montera spektral-TIFF</v>
+        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
+        <v>Montera spektral-TIFF</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
+        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>ch</v>
+        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>Montera och spara</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>Monterar…</v>
+        <v>Montera och spara</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>Monterade {n} kanaler.</v>
+        <v>Monterar…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
+        <v>Monterade {n} kanaler.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>Avbryt</v>
+        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} fil(er) inte inlästa</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
+        <v>{n} fil(er) inte inlästa</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>OK</v>
+        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>eller</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>Välj fil</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>Rubrik</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>Taggar</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>Validering</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>Analys</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% färg</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>Perceptuell</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>Mättnad</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>Profilstatistik</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>medel</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>Analyserar…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>Analys</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>Diagram</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>Rådata</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>Kurvor</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>Ingångskurvor</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>Utgångskurvor</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>CLUT-bild</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>Gamut-bild</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>Kromaticitet</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>Tonkurva</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>Kurvtabell</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>Tabeller</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>Data</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>Utvärdera</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>Läser in…</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>Ingång</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>Utgång</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>Flyttal</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>Normaliserad</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>Läsbar</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>Enhet → PCS</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → Enhet</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>Läser in…</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>Säkerhet</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>Överensstämmelse</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>Kvalitet</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>RAPPORT</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>E-postadress</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>du@exempel.com</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>(valfritt)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>Avbryt</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>Prenumerera</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>Stäng</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>Fel:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2555,1151 +2555,1423 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>Perceptuell</v>
+        <v>L* ut (ton)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>Mättnad</v>
+        <v>Kolorimetri för ytterlägen</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Ytterlägena i profilens återgivningsomfång: substratets vithet, det mörkaste svart den trycker, bläcket som det svarta kostar och var varje nyans når sin mest mättade punkt.</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>Profilstatistik</v>
+        <v>Vitpunkten är färgen vid noll färgmedel — det bara substratet. Svartpunkten tas fram genom att föra PCS-svart (L*=0, a*=b*=0) genom den valda B2A-tabellen för att få den färgmängd profilen väljer för svart, och sedan läsa tillbaka den färgmängden via A2B1. Den totala färgmängden (TAC) är summan av den färgmängden. Absolut kolorimetri visar substratets egen färg; relativ refererar om den till ett perfekt vitt.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Vitpunkt</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Svartpunkt</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>Färgmängd vid svartpunkten</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>medel</v>
+        <v>Den här profilen saknar tagg för mediets vitpunkt, så absolut kolorimetri är inte tillgänglig.</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>Kolorimetri för ytterlägen är endast tillgänglig för utdataprofiler (skrivare) — den förutsätter att noll färgmedel betyder bart substrat.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>max</v>
+        <v>Fullton mot maximal kroma</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>Analyserar…</v>
+        <v>Var varje bläckhörn hamnar, och den mest kromatiska punkten på vägen dit. Mätt via A2B1, så dessa rader ändras inte med renderingsavsikten ovan. I en välartad profil sammanfaller de två raderna; om maximal kroma nås före fullton gör bläcket efter den punkten bara mörkare.</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>Analys</v>
+        <v>Nyans</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Fullton</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>Diagram</v>
+        <v>Max C*</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>Rådata</v>
+        <v>Vid färgmängd</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>Maximal kroma nås före fullton — bläck efter denna punkt gör bara mörkare.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>Bläckförbrukning i skuggor</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>Kurvor</v>
+        <v>Fyra raka banor genom a*b*-planet vid en konstant, medvetet mörk ljushet, förda genom den valda B2A-tabellen. Alla sampel har samma L*, så varje abrupt steg eller omkastning i ett färgmedel kommer enbart från hanteringen av nyans och kroma — signaturen för en gamutmappningsartefakt i skuggorna.</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>Ingångskurvor</v>
+        <v>Bläckförbrukning i skuggor är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>Utgångskurvor</v>
+        <v>Plan med konstant L*</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>CLUT-bild</v>
+        <v>svartpunktskompenserad från</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>Gamut-bild</v>
+        <v>Position längs banan</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>Kromaticitet</v>
+        <v>Bana</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>Tonkurva</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>Kurvtabell</v>
+        <v>Gul</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>Tabeller</v>
+        <v>Röd</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>Data</v>
+        <v>Grön</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>Utvärdera</v>
+        <v>Blå</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>Läser in…</v>
+        <v>Svart</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>Ingång</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>Utgång</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>Flyttal</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>Normaliserad</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>Läsbar</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>Enhet → PCS</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → Enhet</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>Läser in…</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>max</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>Säkerhet</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>Överensstämmelse</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>Kvalitet</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>RAPPORT</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>UNDERKÄND</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>kontroller</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>Prenumerera</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>Stäng</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>E-postadress</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>du@exempel.com</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>(valfritt)</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>Avbryt</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>Prenumerera</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>Stäng</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>Fel:</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>Konvertera till XML</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>Profil-ID</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>Taggnamn</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>Offset</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>Storlek</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>Utfyllnad</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>Typ</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>Array av {type}</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>byte</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>Profilen är giltig</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>Giltig</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>Varning</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>Fel</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>Okänd</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>Godkänd</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>Underkänd</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>Utlöst av</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>Fält</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>Aktuellt värde</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>Krävs: 0</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>Ogiltigt</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>Stäng</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>indrag</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>sortera nycklar</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Ingen valideringsutdata</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>Profilen är giltig</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>Profilen har varning(ar)</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>Profilen följer inte specifikationen</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>Kritiskt valideringsfel</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>Okänd valideringsstatus</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>Kritiskt — visas endast för granskning</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -533,3445 +533,3477 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>Angiven färgrymd</v>
+        <v>Tur-och-retur-ΔE efter ljushet</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (ljushet för den begärda färgen)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>Ej angiven</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>Ej utvärderad</v>
+        <v>punkter, gamutgräns → neutral</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>PRMG-interoperabilitet</v>
+        <v>Angiven färgrymd</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>Tur-och-retur-ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>Antal</v>
+        <v>Ej angiven</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>Andel</v>
+        <v>Ej utvärderad</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>Totalt</v>
+        <v>PRMG-interoperabilitet</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG ej utvärderad</v>
+        <v>Tur-och-retur-ΔE</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>Mätvärden för hela profilen för en renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och ett mått på tur och retur-noggrannheten. Välj renderingsavsikt och typ av tur och retur — tabellen och histogrammet uppdateras därefter.</v>
+        <v>Antal</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>Typ av tur och retur</v>
+        <v>Andel</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>Påverkar inte denna typ av tur och retur</v>
+        <v>Totalt</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>Denna typ av tur och retur är inte tillgänglig för den här profilen.</v>
+        <v>PRMG ej utvärderad</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>Fördelning av tur och retur-ΔE</v>
+        <v>Mätvärden för hela profilen för en renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och ett mått på tur och retur-noggrannheten. Välj renderingsavsikt och typ av tur och retur — tabellen och histogrammet uppdateras därefter.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>Inga tur och retur-prover hamnade inom det utvärderade området.</v>
+        <v>Typ av tur och retur</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>Standardavvikelse</v>
+        <v>Påverkar inte denna typ av tur och retur</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>Relativ frekvens</v>
+        <v>Denna typ av tur och retur är inte tillgänglig för den här profilen.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>Kumulativ frekvens</v>
+        <v>Fördelning av tur och retur-ΔE</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>Horisontell skala</v>
+        <v>Inga tur och retur-prover hamnade inom det utvärderade området.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>Heltals-ΔE</v>
+        <v>Standardavvikelse</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>Autoskala</v>
+        <v>Relativ frekvens</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>Klasser</v>
+        <v>Kumulativ frekvens</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>CLUT-bild</v>
+        <v>Horisontell skala</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>Färguppslagstabellen (CLUT) för en enhet↔PCS-transform, utlagd som en bild. Välj vilken renderingsavsikts-tabell som ska visas.</v>
+        <v>Heltals-ΔE</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>Den här profilen har inga CLUT-baserade enhet↔PCS-tabeller att visualisera.</v>
+        <v>Autoskala</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>Gamut-bild</v>
+        <v>Klasser</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>Gamut-taggens karta över inom/utom gamut: neutral där en PCS-färg är reproducerbar, röd där den hamnar utanför enhetens gamut.</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>Den här profilen har ingen gamut-tagg att visualisera.</v>
+        <v>Färguppslagstabellen (CLUT) för en enhet↔PCS-transform, utlagd som en bild. Välj vilken renderingsavsikts-tabell som ska visas.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>Vertikal skala</v>
+        <v>Den här profilen har inga CLUT-baserade enhet↔PCS-tabeller att visualisera.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>Tonökning</v>
+        <v>Gamut-taggens karta över inom/utom gamut: neutral där en PCS-färg är reproducerbar, röd där den hamnar utanför enhetens gamut.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>Tonökning (ut − in)</v>
+        <v>Den här profilen har ingen gamut-tagg att visualisera.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>Visa fullständig dump</v>
+        <v>Vertikal skala</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>Utdata avkortad av prestandaskäl.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>Översikt inom gamut (RT0)</v>
+        <v>Tonökning</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tonökning (ut − in)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>Reproducerbarhet (RT2)</v>
+        <v>Visa fullständig dump</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>PRMG-interoperabilitet</v>
+        <v>Utdata avkortad av prestandaskäl.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>iccviz-översikt: ett rutnät av enhetsvärden förs till PCS, tillbaka till enhet och till PCS igen; ΔE*ab mäts mellan de två PCS-passen. En snabb stabilitetskontroll inom gamut.</v>
+        <v>Översikt inom gamut (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Tur och retur 1: ΔE*ab mellan varje enhetsfärgs PCS och dess PCS efter en tur och retur Lab → enhet → Lab. Speglar inversionsnoggrannhet och gamutmappning.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip Tur och retur 2: ΔE*ab mellan första och andra tur och retur — hur stabil en upprepad PCS-tur och retur är (reproducerbarhet, oberoende av den första turens gamutklippning).</v>
+        <v>Reproducerbarhet (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG: PCS-färger inom Perceptual Reference Medium Gamut gör en enda tur och retur (Lab → enhet → Lab); ΔE*ab-fördelningen visar interoperabiliteten mellan profiler.</v>
+        <v>PRMG-interoperabilitet</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>Inställningar</v>
+        <v>iccviz-översikt: ett rutnät av enhetsvärden förs till PCS, tillbaka till enhet och till PCS igen; ΔE*ab mäts mellan de två PCS-passen. En snabb stabilitetskontroll inom gamut.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>Visning</v>
+        <v>iccRoundTrip Tur och retur 1: ΔE*ab mellan varje enhetsfärgs PCS och dess PCS efter en tur och retur Lab → enhet → Lab. Speglar inversionsnoggrannhet och gamutmappning.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>Bakgrund</v>
+        <v>iccRoundTrip Tur och retur 2: ΔE*ab mellan första och andra tur och retur — hur stabil en upprepad PCS-tur och retur är (reproducerbarhet, oberoende av den första turens gamutklippning).</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>Språk</v>
+        <v>iccRoundTrip PRMG: PCS-färger inom Perceptual Reference Medium Gamut gör en enda tur och retur (Lab → enhet → Lab); ΔE*ab-fördelningen visar interoperabiliteten mellan profiler.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>System</v>
+        <v>Inställningar</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>Ljus</v>
+        <v>Visning</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>Mörk</v>
+        <v>Bakgrund</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>Systemstandard</v>
+        <v>Språk</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>Talformat</v>
+        <v>System</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>Hexadecimal</v>
+        <v>Ljus</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>Decimal</v>
+        <v>Mörk</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>Hjälp</v>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>Kontakt</v>
+        <v>Talformat</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>Användarhandbok</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>Sök i handboken</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>Sök i användarhandboken</v>
+        <v>Hjälp</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>Föregående träff</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>Nästa träff</v>
+        <v>Användarhandbok</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Stäng handboken</v>
+        <v>Sök i handboken</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>Läser in…</v>
+        <v>Sök i användarhandboken</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>Det gick inte att läsa in användarhandboken.</v>
+        <v>Föregående träff</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>Inga</v>
+        <v>Nästa träff</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Stäng handboken</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v>Baserat på demoimplementeringen</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Det gick inte att läsa in användarhandboken.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>Validerar…</v>
+        <v>Inga</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>Spara ICC-profil</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● Ändrad — osparad</v>
+        <v>Baserat på demoimplementeringen</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>Profiler</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>Visa profilpoolen</v>
+        <v>Validerar…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>Fäll ihop</v>
+        <v>Spara ICC-profil</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>Läs in profiler</v>
+        <v>● Ändrad — osparad</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>Ta bort</v>
+        <v>Profiler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>Släpp ICC-profiler här</v>
+        <v>Visa profilpoolen</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>eller en bild (TIFF/PNG/JPEG) för att extrahera dess inbäddade profil — filerna stannar på din enhet.</v>
+        <v>Fäll ihop</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>Ny från .cube</v>
+        <v>Läs in profiler</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>Sortera efter namn</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>Släpp ICC-profiler här</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>Ny profil från .cube</v>
+        <v>eller en bild (TIFF/PNG/JPEG) för att extrahera dess inbäddade profil — filerna stannar på din enhet.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
+        <v>Ny från .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>Välj .cube-fil</v>
+        <v>Sortera efter namn</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Ny profil från .cube</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Välj .cube-fil</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>eller släpp den här, eller klistra in nedan</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Avbryt</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Skapa DeviceLink</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Skapar…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Det gick inte att läsa den filen.</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>Profil</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>Jämför</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>Länka</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>Spektral</v>
+        <v>Det gick inte att läsa den filen.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>Dra profiler från poolen till den här fliken</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>Ta bort</v>
+        <v>Jämför</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>Ingen profil vald</v>
+        <v>Länka</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>Inget att jämföra ännu</v>
+        <v>Dra profiler från poolen till den här fliken</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>Dra en eller flera profiler till fliken Jämför.</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>Gamutjämförelse</v>
+        <v>Ingen profil vald</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
+        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Inget att jämföra ännu</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>Skal</v>
+        <v>Dra en eller flera profiler till fliken Jämför.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>Trådmodell</v>
+        <v>Gamutjämförelse</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>Axelnummer</v>
+        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacitet</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>Färg</v>
+        <v>Skal</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>Enfärgad</v>
+        <v>Trådmodell</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>Efter värde</v>
+        <v>Axelnummer</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>Efter nyans</v>
+        <v>Opacitet</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotation</v>
+        <v>Färg</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>Skivtallrik</v>
+        <v>Enfärgad</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>Omloppsbana</v>
+        <v>Efter värde</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>Draghastighet</v>
+        <v>Efter nyans</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>Rullning</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>Rullningshastighet</v>
+        <v>Skivtallrik</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>Bygger gamut…</v>
+        <v>Omloppsbana</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>ingen gamut</v>
+        <v>Draghastighet</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>Visa/dölj</v>
+        <v>Rullning</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>3D-gamutskal</v>
+        <v>Rullningshastighet</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>2D-gamutsnitt</v>
+        <v>Bygger gamut…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>Plan</v>
+        <v>ingen gamut</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Visa/dölj</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>3D-gamutskal</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>2D-gamutsnitt</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>Länkning</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4-skärmskapare</v>
+        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
+        <v>Länkning</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB-skärm</v>
+        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>släpp en skärmprofil</v>
+        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>V5-observatör (PCC)</v>
+        <v>V4-skärmskapare</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>släpp en observatörsprofil</v>
+        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
+        <v>V5 RGB-skärm</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Skapa V4-skärmprofil</v>
+        <v>släpp en skärmprofil</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>Profilnamn</v>
+        <v>V5-observatör (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Skapa</v>
+        <v>släpp en observatörsprofil</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>Skapar…</v>
+        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
+        <v>Skapa V4-skärmprofil</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>Länkpipeline</v>
+        <v>Profilnamn</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
+        <v>Skapa</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>Klar</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
+        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>Kontrollerar bild…</v>
+        <v>Länkpipeline</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
+        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
+        <v>Klar</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>Transformera bild</v>
+        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>Transformerar…</v>
+        <v>Kontrollerar bild…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>Släpp profiler för att starta kedjan</v>
+        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>borttagen</v>
+        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>Flytta tidigare</v>
+        <v>Transformera bild</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>Flytta senare</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>Flytta upp</v>
+        <v>Släpp profiler för att starta kedjan</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>Flytta ner</v>
+        <v>borttagen</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>Återgivningsalternativ (alla)</v>
+        <v>Flytta tidigare</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>Återgivningsalternativ för denna transformering</v>
+        <v>Flytta senare</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>Transformeringarna använder olika återgivningsalternativ</v>
+        <v>Flytta upp</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
+        <v>Flytta ner</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
+        <v>Återgivningsalternativ (alla)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>Kedja</v>
+        <v>Återgivningsalternativ för denna transformering</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>Kedjan kunde inte analyseras.</v>
+        <v>Transformeringarna använder olika återgivningsalternativ</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>Kontrollerar kedja…</v>
+        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>Kedjan hänger inte ihop ({detail}).</v>
+        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
+        <v>Kedja</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>Åtgärda kedjan innan bilder bearbetas</v>
+        <v>Kedjan kunde inte analyseras.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>Rensa</v>
+        <v>Kontrollerar kedja…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Kedjan hänger inte ihop ({detail}).</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>DeviceLink-namn</v>
+        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>Skapar…</v>
+        <v>Åtgärda kedjan innan bilder bearbetas</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>Bygg en kedja för att bearbeta bilder</v>
+        <v>DeviceLink-namn</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>Sparade den transformerade bilden.</v>
+        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>Kunde inte läsa filen.</v>
+        <v>Bygg en kedja för att bearbeta bilder</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>Datafilen är för stor.</v>
+        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformera data</v>
+        <v>Sparade den transformerade bilden.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>Transformerar…</v>
+        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>Föredra</v>
+        <v>Kunde inte läsa filen.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>Observatör</v>
+        <v>Datafilen är för stor.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>Ljuskälla</v>
+        <v>Transformera data</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>Villkor</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>Filtrera {n} dubblett(er)</v>
+        <v>Föredra</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>median</v>
+        <v>Observatör</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>medelvärde</v>
+        <v>Ljuskälla</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>patchar</v>
+        <v>Villkor</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} dubbletter</v>
+        <v>Filtrera {n} dubblett(er)</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>Transformeringsresultat</v>
+        <v>median</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · {n} patchar</v>
+        <v>medelvärde</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
+        <v>patchar</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>Spara som</v>
+        <v>{n} dubbletter</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>Spara</v>
+        <v>Transformeringsresultat</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>Invertera transformering</v>
+        <v>{src} → {dst} · {n} patchar</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>Inverterar…</v>
+        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>Invertera</v>
+        <v>Spara som</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>sista steget</v>
+        <v>Spara</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>första steget</v>
+        <v>Invertera transformering</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>Data i {in} → sök {out}</v>
+        <v>Inverterar…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>Invertering kräver en kedja med 2–3 profiler</v>
+        <v>Invertera</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
+        <v>sista steget</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>ΔE-kostnad</v>
+        <v>första steget</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>Denna bild har en inbäddad ICC-profil.</v>
+        <v>Data i {in} → sök {out}</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extrahera och lägg till i kedjan</v>
+        <v>Invertering kräver en kedja med 2–3 profiler</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>Extraherar…</v>
+        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>Avfärda</v>
+        <v>ΔE-kostnad</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
+        <v>Denna bild har en inbäddad ICC-profil.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>Alternativ för bildutdata</v>
+        <v>Extrahera och lägg till i kedjan</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>Kodning</v>
+        <v>Extraherar…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>Samma som källan</v>
+        <v>Avfärda</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8-bitars</v>
+        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16-bitars</v>
+        <v>Alternativ för bildutdata</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>Flyttal (32-bitars)</v>
+        <v>Kodning</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>Komprimering</v>
+        <v>Samma som källan</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>Ingen</v>
+        <v>8-bitars</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>Planformat</v>
+        <v>16-bitars</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>Sammansatt</v>
+        <v>Flyttal (32-bitars)</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>Separerad</v>
+        <v>Komprimering</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>CMM-interpolation</v>
+        <v>Ingen</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>Tetraedrisk</v>
+        <v>Planformat</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>Linjär</v>
+        <v>Sammansatt</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>Bädda in ICC</v>
+        <v>Separerad</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
+        <v>CMM-interpolation</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>Montera spektral-TIFF</v>
+        <v>Tetraedrisk</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
+        <v>Linjär</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
+        <v>Bädda in ICC</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>ch</v>
+        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>Montera och spara</v>
+        <v>Montera spektral-TIFF</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>Monterar…</v>
+        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>Monterade {n} kanaler.</v>
+        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>Avbryt</v>
+        <v>Montera och spara</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n} fil(er) inte inlästa</v>
+        <v>Monterar…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
+        <v>Monterade {n} kanaler.</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>OK</v>
+        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>eller</v>
+        <v>{n} fil(er) inte inlästa</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>Välj fil</v>
+        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>Rubrik</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>Taggar</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>Validering</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>Analys</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% färg</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* ut (ton)</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>Kolorimetri för ytterlägen</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>Ytterlägena i profilens återgivningsomfång: substratets vithet, det mörkaste svart den trycker, bläcket som det svarta kostar och var varje nyans når sin mest mättade punkt.</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>Vitpunkten är färgen vid noll färgmedel — det bara substratet. Svartpunkten tas fram genom att föra PCS-svart (L*=0, a*=b*=0) genom den valda B2A-tabellen för att få den färgmängd profilen väljer för svart, och sedan läsa tillbaka den färgmängden via A2B1. Den totala färgmängden (TAC) är summan av den färgmängden. Absolut kolorimetri visar substratets egen färg; relativ refererar om den till ett perfekt vitt.</v>
+        <v>L* ut (ton)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>Relativ</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>Absolut</v>
+        <v>Kolorimetri för ytterlägen</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>Vitpunkt</v>
+        <v>Ytterlägena i profilens återgivningsomfång: substratets vithet, det mörkaste svart den trycker, bläcket som det svarta kostar och var varje nyans når sin mest mättade punkt.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>Svartpunkt</v>
+        <v>Vitpunkten är färgen vid noll färgmedel — det bara substratet. Svartpunkten tas fram genom att föra PCS-svart (L*=0, a*=b*=0) genom den valda B2A-tabellen för att få den färgmängd profilen väljer för svart, och sedan läsa tillbaka den färgmängden via A2B1. Den totala färgmängden (TAC) är summan av den färgmängden. Absolut kolorimetri visar substratets egen färg; relativ refererar om den till ett perfekt vitt.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>Färgmängd vid svartpunkten</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>Den här profilen saknar tagg för mediets vitpunkt, så absolut kolorimetri är inte tillgänglig.</v>
+        <v>Vitpunkt</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>Kolorimetri för ytterlägen är endast tillgänglig för utdataprofiler (skrivare) — den förutsätter att noll färgmedel betyder bart substrat.</v>
+        <v>Svartpunkt</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Fullton mot maximal kroma</v>
+        <v>Färgmängd vid svartpunkten</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>Var varje bläckhörn hamnar, och den mest kromatiska punkten på vägen dit. Mätt via A2B1, så dessa rader ändras inte med renderingsavsikten ovan. I en välartad profil sammanfaller de två raderna; om maximal kroma nås före fullton gör bläcket efter den punkten bara mörkare.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>Nyans</v>
+        <v>Den här profilen saknar tagg för mediets vitpunkt, så absolut kolorimetri är inte tillgänglig.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>Fullton</v>
+        <v>Kolorimetri för ytterlägen är endast tillgänglig för utdataprofiler (skrivare) — den förutsätter att noll färgmedel betyder bart substrat.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>Max C*</v>
+        <v>Fullton mot maximal kroma</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>Vid färgmängd</v>
+        <v>Var varje bläckhörn hamnar, och den mest kromatiska punkten på vägen dit. Mätt via A2B1, så dessa rader ändras inte med renderingsavsikten ovan. I en välartad profil sammanfaller de två raderna; om maximal kroma nås före fullton gör bläcket efter den punkten bara mörkare.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>Maximal kroma nås före fullton — bläck efter denna punkt gör bara mörkare.</v>
+        <v>Nyans</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>Bläckförbrukning i skuggor</v>
+        <v>Fullton</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>Fyra raka banor genom a*b*-planet vid en konstant, medvetet mörk ljushet, förda genom den valda B2A-tabellen. Alla sampel har samma L*, så varje abrupt steg eller omkastning i ett färgmedel kommer enbart från hanteringen av nyans och kroma — signaturen för en gamutmappningsartefakt i skuggorna.</v>
+        <v>Max C*</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>Bläckförbrukning i skuggor är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Vid färgmängd</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>Plan med konstant L*</v>
+        <v>Maximal kroma nås före fullton — bläck efter denna punkt gör bara mörkare.</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>svartpunktskompenserad från</v>
+        <v>Bläckförbrukning i skuggor</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>Position längs banan</v>
+        <v>Fyra raka banor genom a*b*-planet vid en konstant, medvetet mörk ljushet, förda genom den valda B2A-tabellen. Alla sampel har samma L*, så varje abrupt steg eller omkastning i ett färgmedel kommer enbart från hanteringen av nyans och kroma — signaturen för en gamutmappningsartefakt i skuggorna.</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>Bana</v>
+        <v>Bläckförbrukning i skuggor är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>Cyan</v>
+        <v>Plan med konstant L*</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>Magenta</v>
+        <v>svartpunktskompenserad från</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>Gul</v>
+        <v>Position längs banan</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>Röd</v>
+        <v>Bana</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>Grön</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>Blå</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>Svart</v>
+        <v>Gul</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>Perceptuell</v>
+        <v>Röd</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Grön</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>Mättnad</v>
+        <v>Blå</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Svart</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>Profilstatistik</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>medel</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>max</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>Analyserar…</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>Analys</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>Diagram</v>
+        <v>max</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>Rådata</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>Kurvor</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>Ingångskurvor</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>Utgångskurvor</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>CLUT-bild</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>Gamut-bild</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>Kromaticitet</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>Tonkurva</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>Kurvtabell</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>Tabeller</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>Data</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>Utvärdera</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>Läser in…</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>Ingång</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>Utgång</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>Flyttal</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>Normaliserad</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Läsbar</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>Enhet → PCS</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → Enhet</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>Läser in…</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>Säkerhet</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>Överensstämmelse</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>Kvalitet</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>RAPPORT</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>UNDERKÄND</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>kontroller</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>Drivs av {lib}</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>Prenumerera</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>Stäng</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>E-postadress</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>du@exempel.com</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>(valfritt)</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>Avbryt</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>Prenumerera</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>Stäng</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>Fel:</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>Konvertera till XML</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>Profil-ID</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>Taggnamn</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>Offset</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>Storlek</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>Utfyllnad</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>Typ</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>Array av {type}</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>byte</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>Profilen är giltig</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>Giltig</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>Varning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>Fel</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>Okänd</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>Godkänd</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>Underkänd</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>Utlöst av</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>Fält</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>Aktuellt värde</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>Krävs: 0</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>Ogiltigt</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>Stäng</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>indrag</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>sortera nycklar</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2803,1207 +2803,1343 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>Cyan</v>
+        <v>Primärbläckvägar genom neutralt</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>Magenta</v>
+        <v>Tre vägar inom färgomfånget — cyan→röd, magenta→grön, gul→blå — var och en genom neutralaxeln vid mittljusheten för sina ändpunkter, genom den valda B2A-tabellen. Varje sampel ligger inom omfånget, så till skillnad från skuggvägarna är varje plötsligt steg eller omkastning i ett färgämne ett CLUT-jämnhetsfel snarare än en omfångsmappningsartefakt.</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>Gul</v>
+        <v>Primärbläckvägar är endast tillgängliga för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>Röd</v>
+        <v>Position längs vägen (neutralt i mitten)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>Grön</v>
+        <v>Svartpunktskompensation tillämpad för denna återgivning.</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>Blå</v>
+        <v>Statistik för färgförbrukning</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>Svart</v>
+        <v>Hur mycket av varje färgämne profilen lägger på, som summa och som andel av totalen — separationens signatur för färgförbrukning.</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>Perceptuell</v>
+        <v>Statistik för färgförbrukning är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Neutralaxel</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>Mättnad</v>
+        <v>Medeltäckning</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Färgandel</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>Profilstatistik</v>
+        <v>Färgandelen är fingeravtrycket för neutraluppbyggnaden — varje färgämnes andel av den totala pålagda färgen, oberoende av antalet sampel.</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Punkter inom omfånget</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Färgförbrukning över alla färger i omfånget kräver B2A-omfångsgränsen, som ännu inte är byggd — kommer senare.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Inga färgämnesdata att sammanfatta.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Välj en B2A-tabell (PCS→enhet) nedan för att även visa en gråskalebild av färgtäckningen för varje färgämne.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>Färgtäckning för varje färgämne över samma gitter (mörkare = mer färg).</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>medel</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>Gul</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>max</v>
+        <v>Röd</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>Analyserar…</v>
+        <v>Grön</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>Analys</v>
+        <v>Blå</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Svart</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>Diagram</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>Rådata</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>Kurvor</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>Ingångskurvor</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>Utgångskurvor</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>CLUT-bild</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>Gamut-bild</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>Kromaticitet</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>Tonkurva</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>Kurvtabell</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>Tabeller</v>
+        <v>max</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>Data</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>Utvärdera</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>Läser in…</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>Ingång</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Utgång</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>Flyttal</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>Rutnätspunkt</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>Normaliserad</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Läsbar</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Enhet → PCS</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → Enhet</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>Läser in…</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>Säkerhet</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>Överensstämmelse</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>Kvalitet</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>RAPPORT</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>UNDERKÄND</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>kontroller</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>Prenumerera</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>Stäng</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>E-postadress</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>du@exempel.com</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>(valfritt)</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>Avbryt</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>Prenumerera</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>Stäng</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>Fel:</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>Konvertera till XML</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>Konvertera till ICC</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>Konverterar till XML…</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>Profil-ID</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>Taggnamn</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>Offset</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>Storlek</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Utfyllnad</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>Typ</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>Array av {type}</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>byte</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>Profilen är giltig</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>Giltig</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>Varning</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>Fel</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>Okänd</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>Godkänd</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>Underkänd</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>Utlöst av</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>Fält</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>Aktuellt värde</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>Krävs: 0</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>Ogiltigt</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>Stäng</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>indrag</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>sortera nycklar</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
   </ignoredErrors>
 </worksheet>
 </file>